--- a/B4_配對診斷.xlsx
+++ b/B4_配對診斷.xlsx
@@ -10,7 +10,8 @@
     <sheet name="刻度一致性" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="牙位衍生方法_未校正" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="排除清單" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="完整合併表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="未匹配清單" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="完整合併表" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,174 +584,240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF55"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>圖片檔名</t>
+          <t>醫師檔名</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>縮放比scale</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>原圖寬</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>原圖高</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>mask狀態</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>偵測到mask數</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>選取方式</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>GT格式</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>兩法選取一致</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>mask_IoU_vs_GT框</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>次佳mask_IoU</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>長軸解釋比</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>方向依據</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>寬度法方向一致</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>兩端寬度比</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>AB長度_mask幾何_letterbox px</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>AB長度_mask幾何_原圖px</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>冠寬_letterbox px</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>冠寬_原圖px</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>冠寬位置_距A端比例</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>長寬比_mask幾何÷冠寬</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>QC備註</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>建議人工複查</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>醫師檔名</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>填充物長度(mm)</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>牙位</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>醫師備註（選填）</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>長寬比</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>X_冠寬比例尺_mm</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>X_牙位基準_mm</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>資料夾來源</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>折數fold</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>033.jpg</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>035.jpg</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>053.jpg</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>圖片檔名</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>縮放比scale</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>原圖寬</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>原圖高</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>mask狀態</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>偵測到mask數</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>選取方式</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>GT格式</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>兩法選取一致</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mask_IoU_vs_GT框</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>次佳mask_IoU</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>長軸解釋比</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>方向依據</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>寬度法方向一致</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>兩端寬度比</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>AB長度_mask幾何_letterbox px</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>AB長度_mask幾何_原圖px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>冠寬_letterbox px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>冠寬_原圖px</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>冠寬位置_距A端比例</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>長寬比_mask幾何÷冠寬</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>QC備註</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>建議人工複查</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>醫師檔名</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>填充物長度(mm)</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>牙位</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>醫師備註（選填）</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>年齡</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>性別</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>長寬比</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>X_冠寬比例尺_mm</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>X_牙位基準_mm</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>資料夾來源</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>折數fold</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>001_jpg.rf.f66116916f1034ff42d3ca622244a7a1.jpg</t>
         </is>
       </c>
@@ -841,20 +908,28 @@
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
         <v>3.266873158506411</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>21.23467553029167</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>22</v>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -955,20 +1030,28 @@
         </is>
       </c>
       <c r="AB3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
         <v>2.371454051349239</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>20.15735943646853</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1065,20 +1148,28 @@
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
         <v>2.889551909981215</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>24.56119123484033</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1179,20 +1270,28 @@
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
         <v>3.571431171984934</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>17.85715585992467</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>21</v>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1289,20 +1388,28 @@
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
         <v>2.955749959178929</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>19.21237473466304</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>22</v>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1399,20 +1506,28 @@
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
         <v>2.910241371188036</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>24.73705165509831</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1513,20 +1628,28 @@
         </is>
       </c>
       <c r="AB8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
         <v>3.476504996811129</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>29.5502924728946</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1623,20 +1746,28 @@
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
+        <v>64</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
         <v>3.217680163942306</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>20.91492106562499</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>22</v>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1733,20 +1864,28 @@
       </c>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
         <v>3.199496850888926</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>20.79672953077802</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>22</v>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1847,20 +1986,28 @@
       </c>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
         <v>3.205589070659406</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>16.02794535329703</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>21</v>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1957,20 +2104,28 @@
       </c>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
         <v>2.946636523342565</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>25.0464104484118</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2071,20 +2226,28 @@
       </c>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD13" t="n">
         <v>2.993678765477374</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>19.45891197560293</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>22</v>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2181,20 +2344,28 @@
       </c>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD14" t="n">
         <v>3.101752717391304</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>26.36489809782609</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2291,20 +2462,28 @@
       </c>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD15" t="n">
         <v>3.970618951612903</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AE15" t="n">
         <v>19.85309475806451</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>21</v>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF15" t="n">
+      <c r="AH15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2401,20 +2580,28 @@
       </c>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
         <v>4.494056034482758</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>22.47028017241379</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>21</v>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF16" t="n">
+      <c r="AH16" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2511,20 +2698,28 @@
       </c>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="n">
+        <v>49</v>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
         <v>4.136764504758082</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AE17" t="n">
         <v>20.68382252379041</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>21</v>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF17" t="n">
+      <c r="AH17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2621,20 +2816,28 @@
       </c>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
         <v>2.990926955416433</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>25.42287912103968</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF18" t="n">
+      <c r="AH18" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2731,20 +2934,28 @@
       </c>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="n">
+        <v>47</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
         <v>3.270542151162791</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>21.25852398255814</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>22</v>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2845,20 +3056,28 @@
       </c>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD20" t="n">
         <v>3.25857527811456</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>27.69788986397376</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2959,20 +3178,28 @@
       </c>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD21" t="n">
         <v>2.511132888768736</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AE21" t="n">
         <v>21.34462955453426</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF21" t="n">
+      <c r="AH21" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3069,20 +3296,28 @@
       </c>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
         <v>3.001643895348837</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AE22" t="n">
         <v>19.51068531976744</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>22</v>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF22" t="n">
+      <c r="AH22" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3183,20 +3418,28 @@
       </c>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
         <v>2.840766824648152</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>24.14651800950929</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF23" t="n">
+      <c r="AH23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3297,20 +3540,28 @@
       </c>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
         <v>2.312922603200779</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>19.65984212720662</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE24" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3411,20 +3662,28 @@
       </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
         <v>2.698665302695452</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>17.54132446752044</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>22</v>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3525,20 +3784,28 @@
       </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
         <v>5.397867319524392</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>26.98933659762196</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>21</v>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3639,20 +3906,28 @@
       </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
         <v>2.648487978714716</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>22.51214781907508</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3753,20 +4028,28 @@
       </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
         <v>2.974370288707842</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>25.28214745401666</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3867,20 +4150,28 @@
       </c>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="n">
+        <v>41</v>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
         <v>2.850150186320441</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>24.22627658372375</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3977,20 +4268,28 @@
       </c>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="n">
+        <v>52</v>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
         <v>2.730636652861542</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>23.2104115493231</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4087,20 +4386,28 @@
       </c>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
         <v>2.822554311101587</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>23.99171164436349</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4201,20 +4508,28 @@
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD32" t="n">
         <v>2.88000029999925</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>24.48000254999362</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE32" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4315,20 +4630,28 @@
       </c>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD33" t="n">
         <v>2.945617288260959</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>25.03774695021815</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE33" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF33" t="n">
+      <c r="AH33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4429,20 +4752,28 @@
       </c>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="n">
+        <v>59</v>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD34" t="n">
         <v>3.689743125553609</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>23.98333031609846</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>22</v>
       </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4543,20 +4874,28 @@
       </c>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="n">
+        <v>59</v>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD35" t="n">
         <v>3.489177083333333</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
         <v>22.67965104166666</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AF35" t="n">
         <v>22</v>
       </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4653,20 +4992,28 @@
       </c>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD36" t="n">
         <v>2.665649352047868</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>22.65801949240688</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE36" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF36" t="n">
+      <c r="AH36" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4763,20 +5110,28 @@
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD37" t="n">
         <v>3.043865725137255</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AE37" t="n">
         <v>19.78512721339216</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>22</v>
       </c>
-      <c r="AE37" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4877,20 +5232,28 @@
       </c>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD38" t="n">
         <v>3.018166688929766</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>25.65441685590301</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE38" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF38" t="n">
+      <c r="AH38" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4991,20 +5354,28 @@
       </c>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD39" t="n">
         <v>2.327353126826962</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AE39" t="n">
         <v>19.78250157802918</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AF39" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE39" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF39" t="n">
+      <c r="AH39" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5105,20 +5476,28 @@
       </c>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD40" t="n">
         <v>2.890368332106098</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>24.56813082290183</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE40" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5219,20 +5598,28 @@
       </c>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD41" t="n">
         <v>3.712780732050509</v>
       </c>
-      <c r="AC41" t="n">
+      <c r="AE41" t="n">
         <v>24.13307475832831</v>
       </c>
-      <c r="AD41" t="n">
+      <c r="AF41" t="n">
         <v>22</v>
       </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF41" t="n">
+      <c r="AH41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5329,20 +5716,28 @@
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="n">
+        <v>53</v>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD42" t="n">
         <v>3.102696278812628</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>20.16752581228209</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>22</v>
       </c>
-      <c r="AE42" t="inlineStr">
+      <c r="AG42" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5443,20 +5838,28 @@
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AD43" t="n">
         <v>3.834823345129663</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
         <v>19.17411672564831</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AF43" t="n">
         <v>21</v>
       </c>
-      <c r="AE43" t="inlineStr">
+      <c r="AG43" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF43" t="n">
+      <c r="AH43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5557,20 +5960,28 @@
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD44" t="n">
         <v>3.57959925946557</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>19.68779592706063</v>
       </c>
-      <c r="AD44" t="n">
+      <c r="AF44" t="n">
         <v>22</v>
       </c>
-      <c r="AE44" t="inlineStr">
+      <c r="AG44" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF44" t="n">
+      <c r="AH44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5667,20 +6078,28 @@
       </c>
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD45" t="n">
         <v>4.224296204459445</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AE45" t="n">
         <v>21.12148102229722</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AF45" t="n">
         <v>21</v>
       </c>
-      <c r="AE45" t="inlineStr">
+      <c r="AG45" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF45" t="n">
+      <c r="AH45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5781,20 +6200,28 @@
       </c>
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD46" t="n">
         <v>2.312537585775599</v>
       </c>
-      <c r="AC46" t="n">
+      <c r="AE46" t="n">
         <v>19.65656947909259</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE46" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF46" t="n">
+      <c r="AH46" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5895,20 +6322,28 @@
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD47" t="n">
         <v>2.663782221088502</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AE47" t="n">
         <v>22.64214887925227</v>
       </c>
-      <c r="AD47" t="n">
+      <c r="AF47" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE47" t="inlineStr">
+      <c r="AG47" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF47" t="n">
+      <c r="AH47" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6009,20 +6444,28 @@
       </c>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD48" t="n">
         <v>2.46535067925096</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
         <v>20.95548077363316</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AF48" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE48" t="inlineStr">
+      <c r="AG48" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6119,20 +6562,28 @@
       </c>
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD49" t="n">
         <v>3.425476744186047</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AE49" t="n">
         <v>22.2655988372093</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AF49" t="n">
         <v>22</v>
       </c>
-      <c r="AE49" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF49" t="n">
+      <c r="AH49" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6233,20 +6684,28 @@
       </c>
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD50" t="n">
         <v>2.713713364978444</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AE50" t="n">
         <v>23.06656360231677</v>
       </c>
-      <c r="AD50" t="n">
+      <c r="AF50" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE50" t="inlineStr">
+      <c r="AG50" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF50" t="n">
+      <c r="AH50" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6343,20 +6802,28 @@
       </c>
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD51" t="n">
         <v>2.809653273596589</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AE51" t="n">
         <v>23.88205282557101</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AF51" t="n">
         <v>23.5</v>
       </c>
-      <c r="AE51" t="inlineStr">
+      <c r="AG51" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF51" t="n">
+      <c r="AH51" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6457,20 +6924,28 @@
       </c>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD52" t="n">
         <v>3.416478628278818</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AE52" t="n">
         <v>18.7906324555335</v>
       </c>
-      <c r="AD52" t="n">
+      <c r="AF52" t="n">
         <v>22</v>
       </c>
-      <c r="AE52" t="inlineStr">
+      <c r="AG52" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF52" t="n">
+      <c r="AH52" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6567,20 +7042,28 @@
       </c>
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD53" t="n">
         <v>3.596920552176851</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AE53" t="n">
         <v>17.98460276088426</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AF53" t="n">
         <v>21</v>
       </c>
-      <c r="AE53" t="inlineStr">
+      <c r="AG53" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF53" t="n">
+      <c r="AH53" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6681,20 +7164,28 @@
       </c>
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD54" t="n">
         <v>3.687065131026904</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AE54" t="n">
         <v>18.43532565513452</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AF54" t="n">
         <v>21</v>
       </c>
-      <c r="AE54" t="inlineStr">
+      <c r="AG54" t="inlineStr">
         <is>
           <t>train</t>
         </is>
       </c>
-      <c r="AF54" t="n">
+      <c r="AH54" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6799,20 +7290,28 @@
         </is>
       </c>
       <c r="AB55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AD55" t="n">
         <v>2.93997526862059</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AE55" t="n">
         <v>16.16986397741325</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AF55" t="n">
         <v>22</v>
       </c>
-      <c r="AE55" t="inlineStr">
+      <c r="AG55" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="AF55" t="n">
+      <c r="AH55" t="n">
         <v>5</v>
       </c>
     </row>

--- a/B4_配對診斷.xlsx
+++ b/B4_配對診斷.xlsx
@@ -8401,7 +8401,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>067_d0_jpg.rf.d69e1bebfb7e4f8d986ef8037968ad4d.jpg</t>
+          <t>067_d0_jpg.rf.ac90bce7f88c1b868e5f95777451272a.jpg</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0.84</v>
+        <v>0.971</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
